--- a/Packages/cn.etetet.yiuilubangen/Luban/Localhost/Datas/StartScene.xlsx
+++ b/Packages/cn.etetet.yiuilubangen/Luban/Localhost/Datas/StartScene.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>Map2</t>
+  </si>
+  <si>
+    <t>UnitCache</t>
   </si>
 </sst>
 </file>
@@ -16840,8 +16843,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CUA8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1:CUA9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="14.25" spans="1:2575">
       <c r="A1" s="4" t="s">
@@ -24711,6 +24714,24 @@
       </c>
       <c r="G8" s="6"/>
     </row>
+    <row r="9" ht="14.25" spans="2:7">
+      <c r="B9" s="6">
+        <v>306</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Packages/cn.etetet.yiuilubangen/Luban/Localhost/Datas/StartScene.xlsx
+++ b/Packages/cn.etetet.yiuilubangen/Luban/Localhost/Datas/StartScene.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="2"/>
+    <workbookView windowWidth="21600" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Router" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>Realm</t>
+  </si>
+  <si>
+    <t>ArchiveCenter</t>
   </si>
   <si>
     <t>Gate</t>
@@ -9014,8 +9017,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CUA5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:CUA6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="7.25" customWidth="1"/>
     <col min="4" max="4" width="7.125" customWidth="1"/>
@@ -16834,6 +16837,24 @@
         <v>20102</v>
       </c>
     </row>
+    <row r="6" ht="14.25" spans="2:7">
+      <c r="B6" s="6">
+        <v>203</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1000</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -24630,10 +24651,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="6">
         <v>30101</v>
@@ -24651,10 +24672,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="6">
         <v>30102</v>
@@ -24671,10 +24692,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" s="6"/>
     </row>
@@ -24689,10 +24710,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7" s="6"/>
     </row>
@@ -24707,10 +24728,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" s="6"/>
     </row>
@@ -24725,10 +24746,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G9" s="6"/>
     </row>
